--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2350" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="465">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -636,6 +636,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>Timing.repeat.bounds[x]</t>
   </si>
   <si>
@@ -719,6 +722,26 @@
     <t>DR.2</t>
   </si>
   <si>
+    <t>Dosage.timing.repeat.bounds[x]:boundsDuration</t>
+  </si>
+  <si>
+    <t>boundsDuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duration
+</t>
+  </si>
+  <si>
+    <t>Dosage.timing.repeat.bounds[x]:boundsRange</t>
+  </si>
+  <si>
+    <t>boundsRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
+  </si>
+  <si>
     <t>Dosage.timing.repeat.count</t>
   </si>
   <si>
@@ -1016,9 +1039,6 @@
     <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>.outboundRelationship[typeCode=PRCN].target[classCode=OBS, moodCode=EVN, code="as needed"].value=boolean or codable concept</t>
   </si>
   <si>
@@ -1183,10 +1203,6 @@
   </si>
   <si>
     <t>doseRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range
-</t>
   </si>
   <si>
     <t>Dosierungsspanne wird mit low und high angegeben, z.B. 5-10 mg.</t>
@@ -1422,6 +1438,10 @@
   </si>
   <si>
     <t>The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>not supported</t>
@@ -1757,7 +1777,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL68"/>
+  <dimension ref="A1:AL70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="true" bestFit="true"/>
@@ -4363,10 +4383,10 @@
         <v>20</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>94</v>
+        <v>197</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -4381,7 +4401,7 @@
         <v>79</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>20</v>
@@ -4389,13 +4409,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>20</v>
@@ -4417,7 +4437,7 @@
         <v>126</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>194</v>
@@ -4474,7 +4494,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -4489,7 +4509,7 @@
         <v>79</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>20</v>
@@ -4497,10 +4517,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4603,10 +4623,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4711,10 +4731,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4740,13 +4760,13 @@
         <v>170</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4796,7 +4816,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4805,24 +4825,24 @@
         <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4848,20 +4868,20 @@
         <v>170</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q29" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R29" t="s" s="2">
         <v>20</v>
@@ -4906,7 +4926,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4915,26 +4935,28 @@
         <v>82</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>20</v>
       </c>
@@ -4955,20 +4977,16 @@
         <v>126</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5016,7 +5034,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -5031,7 +5049,7 @@
         <v>79</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>20</v>
@@ -5039,12 +5057,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5065,13 +5085,13 @@
         <v>126</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5122,7 +5142,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -5137,7 +5157,7 @@
         <v>79</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
@@ -5145,10 +5165,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5171,19 +5191,19 @@
         <v>126</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5232,7 +5252,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -5247,7 +5267,7 @@
         <v>79</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>20</v>
@@ -5255,10 +5275,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5281,20 +5301,16 @@
         <v>126</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O33" t="s" s="2">
         <v>241</v>
       </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5342,7 +5358,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -5357,7 +5373,7 @@
         <v>79</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>20</v>
@@ -5365,10 +5381,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5391,16 +5407,20 @@
         <v>126</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5424,13 +5444,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5448,7 +5468,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5463,7 +5483,7 @@
         <v>79</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>20</v>
@@ -5471,10 +5491,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5497,22 +5517,24 @@
         <v>126</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q35" t="s" s="2">
-        <v>259</v>
-      </c>
+      <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5556,7 +5578,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5571,7 +5593,7 @@
         <v>79</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
@@ -5579,10 +5601,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5605,13 +5627,13 @@
         <v>126</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5638,13 +5660,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5662,7 +5684,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -5677,18 +5699,18 @@
         <v>79</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5702,7 +5724,7 @@
         <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
@@ -5711,20 +5733,22 @@
         <v>126</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q37" s="2"/>
+      <c r="Q37" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="R37" t="s" s="2">
         <v>20</v>
       </c>
@@ -5768,7 +5792,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5783,7 +5807,7 @@
         <v>79</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -5791,10 +5815,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5817,13 +5841,13 @@
         <v>126</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5874,7 +5898,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5889,18 +5913,18 @@
         <v>79</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5914,7 +5938,7 @@
         <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
@@ -5923,13 +5947,13 @@
         <v>126</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5956,11 +5980,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>276</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -5978,7 +6004,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5993,7 +6019,7 @@
         <v>79</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
@@ -6001,10 +6027,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6015,7 +6041,7 @@
         <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6027,17 +6053,15 @@
         <v>126</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6062,11 +6086,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y40" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z40" t="s" s="2">
-        <v>282</v>
+        <v>20</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6084,13 +6110,13 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
@@ -6099,7 +6125,7 @@
         <v>79</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>87</v>
+        <v>250</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
@@ -6107,10 +6133,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6118,10 +6144,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6133,17 +6159,15 @@
         <v>126</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6168,13 +6192,11 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>20</v>
+        <v>283</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6192,13 +6214,13 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
@@ -6207,18 +6229,18 @@
         <v>79</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>87</v>
+        <v>262</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6232,7 +6254,7 @@
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
@@ -6241,20 +6263,18 @@
         <v>126</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6280,11 +6300,9 @@
       <c r="X42" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="Y42" t="s" s="2">
-        <v>295</v>
-      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6302,7 +6320,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -6317,18 +6335,18 @@
         <v>79</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>298</v>
+        <v>87</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6336,13 +6354,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>20</v>
@@ -6351,15 +6369,17 @@
         <v>126</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6408,13 +6428,13 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
@@ -6423,18 +6443,18 @@
         <v>79</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>304</v>
+        <v>87</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6445,10 +6465,10 @@
         <v>74</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>20</v>
@@ -6457,18 +6477,20 @@
         <v>126</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>116</v>
+        <v>256</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
       </c>
@@ -6492,13 +6514,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>309</v>
+        <v>120</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6516,13 +6538,13 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
@@ -6531,18 +6553,18 @@
         <v>79</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6556,7 +6578,7 @@
         <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>20</v>
@@ -6565,17 +6587,15 @@
         <v>126</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6600,29 +6620,31 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>319</v>
+        <v>20</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>320</v>
+        <v>20</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AC45" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>321</v>
+        <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6637,22 +6659,20 @@
         <v>79</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>323</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>20</v>
       </c>
@@ -6664,7 +6684,7 @@
         <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>20</v>
@@ -6673,16 +6693,16 @@
         <v>126</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6708,13 +6728,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>20</v>
+        <v>317</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -6732,7 +6752,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6747,22 +6767,20 @@
         <v>79</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>323</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>20</v>
       </c>
@@ -6771,7 +6789,7 @@
         <v>74</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -6783,16 +6801,16 @@
         <v>126</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>116</v>
+        <v>322</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6821,28 +6839,26 @@
         <v>149</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
@@ -6857,20 +6873,22 @@
         <v>79</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>330</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>20</v>
       </c>
@@ -6882,7 +6900,7 @@
         <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>20</v>
@@ -6891,20 +6909,18 @@
         <v>126</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>116</v>
+        <v>322</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -6928,13 +6944,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -6952,7 +6968,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
@@ -6967,20 +6983,22 @@
         <v>79</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>20</v>
       </c>
@@ -6989,10 +7007,10 @@
         <v>74</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>20</v>
@@ -7004,15 +7022,15 @@
         <v>116</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7036,11 +7054,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7058,7 +7078,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -7073,18 +7093,18 @@
         <v>79</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>345</v>
+        <v>329</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7098,7 +7118,7 @@
         <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>20</v>
@@ -7110,16 +7130,16 @@
         <v>116</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7147,10 +7167,10 @@
         <v>149</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7168,7 +7188,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
@@ -7183,18 +7203,18 @@
         <v>79</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7217,16 +7237,18 @@
         <v>126</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
       </c>
@@ -7250,13 +7272,11 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7274,13 +7294,13 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
@@ -7289,18 +7309,18 @@
         <v>79</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>20</v>
+        <v>350</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7314,25 +7334,29 @@
         <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>84</v>
+        <v>353</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
@@ -7356,13 +7380,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>20</v>
+        <v>357</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>20</v>
+        <v>358</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7380,7 +7404,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>86</v>
+        <v>352</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7392,54 +7416,52 @@
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>87</v>
+        <v>359</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>20</v>
+        <v>360</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>166</v>
+        <v>362</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>129</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7476,19 +7498,19 @@
         <v>20</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>95</v>
+        <v>361</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7500,21 +7522,21 @@
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>20</v>
+        <v>364</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7534,21 +7556,19 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>362</v>
+        <v>84</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>363</v>
+        <v>85</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>364</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
@@ -7572,13 +7592,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>365</v>
+        <v>20</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>366</v>
+        <v>20</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -7596,7 +7616,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>361</v>
+        <v>86</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>74</v>
@@ -7608,32 +7628,32 @@
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>367</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -7642,23 +7662,21 @@
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>369</v>
+        <v>89</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>370</v>
+        <v>166</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>371</v>
+        <v>167</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
       </c>
@@ -7694,47 +7712,47 @@
         <v>20</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AC55" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="AD55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>321</v>
+        <v>94</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>368</v>
+        <v>95</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>353</v>
+        <v>87</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>374</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>20</v>
       </c>
@@ -7746,7 +7764,7 @@
         <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>20</v>
@@ -7755,19 +7773,17 @@
         <v>126</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>377</v>
+        <v>116</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -7792,13 +7808,13 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>20</v>
+        <v>372</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -7816,7 +7832,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -7831,22 +7847,20 @@
         <v>79</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>353</v>
+        <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
         <v>374</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>379</v>
-      </c>
       <c r="B57" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>20</v>
       </c>
@@ -7858,7 +7872,7 @@
         <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>20</v>
@@ -7867,19 +7881,19 @@
         <v>126</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -7916,19 +7930,17 @@
         <v>20</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
@@ -7943,20 +7955,22 @@
         <v>79</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>374</v>
       </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C58" s="2"/>
+      <c r="C58" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="D58" t="s" s="2">
         <v>20</v>
       </c>
@@ -7968,25 +7982,29 @@
         <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>83</v>
+        <v>230</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>84</v>
+        <v>383</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
       </c>
@@ -8034,7 +8052,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>86</v>
+        <v>374</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
@@ -8046,55 +8064,59 @@
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>87</v>
+        <v>359</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C59" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="B59" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>89</v>
+        <v>386</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>166</v>
+        <v>387</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>167</v>
+        <v>377</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
       </c>
@@ -8130,45 +8152,45 @@
         <v>20</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>95</v>
+        <v>374</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>87</v>
+        <v>359</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8188,23 +8210,19 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>237</v>
+        <v>83</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -8252,7 +8270,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>393</v>
+        <v>86</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>74</v>
@@ -8264,61 +8282,59 @@
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>394</v>
+        <v>87</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>395</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>249</v>
+        <v>89</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>398</v>
+        <v>166</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q61" t="s" s="2">
-        <v>401</v>
-      </c>
+      <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
         <v>20</v>
       </c>
@@ -8338,57 +8354,57 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>402</v>
+        <v>20</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>403</v>
+        <v>20</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>404</v>
+        <v>95</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>405</v>
+        <v>87</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>406</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8411,17 +8427,19 @@
         <v>126</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>83</v>
+        <v>244</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="O62" t="s" s="2">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -8446,11 +8464,13 @@
         <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -8468,7 +8488,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>74</v>
@@ -8483,18 +8503,18 @@
         <v>79</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>415</v>
+        <v>400</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8505,34 +8525,36 @@
         <v>74</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>126</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q63" s="2"/>
+      <c r="Q63" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="R63" t="s" s="2">
         <v>20</v>
       </c>
@@ -8552,13 +8574,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>20</v>
+        <v>407</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>20</v>
+        <v>408</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -8576,7 +8598,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>74</v>
@@ -8585,24 +8607,24 @@
         <v>82</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>422</v>
+        <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8625,19 +8647,17 @@
         <v>126</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>249</v>
+        <v>83</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -8662,13 +8682,11 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>20</v>
+        <v>417</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -8686,7 +8704,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>74</v>
@@ -8701,18 +8719,18 @@
         <v>79</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8735,19 +8753,17 @@
         <v>126</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>433</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -8796,7 +8812,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>74</v>
@@ -8805,24 +8821,24 @@
         <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>20</v>
+        <v>427</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>439</v>
+        <v>420</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8845,19 +8861,19 @@
         <v>126</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>441</v>
+        <v>256</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -8906,7 +8922,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>74</v>
@@ -8921,18 +8937,18 @@
         <v>79</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>447</v>
+        <v>420</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8955,19 +8971,19 @@
         <v>126</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -9016,7 +9032,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>74</v>
@@ -9031,18 +9047,18 @@
         <v>79</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>20</v>
+        <v>444</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9065,17 +9081,19 @@
         <v>126</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L68" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -9124,7 +9142,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>74</v>
@@ -9139,14 +9157,232 @@
         <v>79</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K69" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="L69" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AL70" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL68">
+  <autoFilter ref="A1:AL70">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9156,7 +9392,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI67">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$81</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2795" uniqueCount="525">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1102,13 +1102,194 @@
     <t>A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
+    <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>.routeCode</t>
+  </si>
+  <si>
+    <t>RXR-1</t>
+  </si>
+  <si>
+    <t>Dosage.route.id</t>
+  </si>
+  <si>
+    <t>Dosage.route.extension</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.id</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.extension</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
     <t>https://termgit.elga.gv.at/CodeSystem/medikationartanwendung</t>
   </si>
   <si>
-    <t>.routeCode</t>
-  </si>
-  <si>
-    <t>RXR-1</t>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Dosage.route.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Dosage.method</t>
@@ -1777,7 +1958,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL70"/>
+  <dimension ref="A1:AL81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="true" bestFit="true"/>
@@ -1816,7 +1997,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="109.8359375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7272,11 +7453,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7309,18 +7492,18 @@
         <v>79</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7334,29 +7517,25 @@
         <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>353</v>
+        <v>84</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
@@ -7380,13 +7559,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>357</v>
+        <v>20</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7404,7 +7583,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>352</v>
+        <v>86</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7416,52 +7595,54 @@
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>359</v>
+        <v>87</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>360</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>177</v>
+        <v>89</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>362</v>
+        <v>166</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7498,19 +7679,19 @@
         <v>20</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>361</v>
+        <v>95</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7522,21 +7703,21 @@
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>364</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7547,7 +7728,7 @@
         <v>74</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -7556,19 +7737,23 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
@@ -7616,44 +7801,44 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>86</v>
+        <v>361</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>87</v>
+        <v>362</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>20</v>
+        <v>363</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -7665,17 +7850,15 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>166</v>
+        <v>84</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>129</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -7712,31 +7895,31 @@
         <v>20</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>87</v>
@@ -7747,21 +7930,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -7770,21 +7953,21 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>368</v>
+        <v>166</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>20</v>
       </c>
@@ -7808,57 +7991,57 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>371</v>
+        <v>20</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>372</v>
+        <v>20</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>367</v>
+        <v>95</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7881,19 +8064,19 @@
         <v>126</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>375</v>
+        <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -7903,7 +8086,7 @@
         <v>20</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>20</v>
@@ -7930,17 +8113,19 @@
         <v>20</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AC57" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
@@ -7955,22 +8140,20 @@
         <v>79</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>20</v>
       </c>
@@ -7982,7 +8165,7 @@
         <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>20</v>
@@ -7991,10 +8174,10 @@
         <v>126</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>230</v>
+        <v>83</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="M58" t="s" s="2">
         <v>377</v>
@@ -8002,9 +8185,7 @@
       <c r="N58" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="O58" t="s" s="2">
-        <v>379</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>20</v>
       </c>
@@ -8052,7 +8233,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
@@ -8067,22 +8248,20 @@
         <v>79</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>20</v>
       </c>
@@ -8094,7 +8273,7 @@
         <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>20</v>
@@ -8103,19 +8282,17 @@
         <v>126</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>386</v>
+        <v>256</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8164,7 +8341,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
@@ -8179,15 +8356,15 @@
         <v>79</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>389</v>
@@ -8210,19 +8387,21 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>85</v>
+        <v>391</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -8270,7 +8449,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>86</v>
+        <v>393</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>74</v>
@@ -8282,32 +8461,32 @@
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>87</v>
+        <v>394</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>20</v>
+        <v>395</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -8316,21 +8495,23 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>89</v>
+        <v>322</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>166</v>
+        <v>397</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>167</v>
+        <v>398</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
       </c>
@@ -8366,45 +8547,45 @@
         <v>20</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>95</v>
+        <v>401</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>87</v>
+        <v>402</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>20</v>
+        <v>403</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8427,19 +8608,19 @@
         <v>126</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>244</v>
+        <v>83</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -8488,7 +8669,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>74</v>
@@ -8503,18 +8684,18 @@
         <v>79</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8525,36 +8706,36 @@
         <v>74</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>126</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>256</v>
+        <v>116</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q63" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
         <v>20</v>
       </c>
@@ -8574,13 +8755,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -8598,7 +8779,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>74</v>
@@ -8613,18 +8794,18 @@
         <v>79</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8638,7 +8819,7 @@
         <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>20</v>
@@ -8647,18 +8828,16 @@
         <v>126</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>83</v>
+        <v>177</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>416</v>
-      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>20</v>
       </c>
@@ -8682,11 +8861,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>417</v>
+        <v>20</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -8704,13 +8885,13 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
@@ -8719,18 +8900,18 @@
         <v>79</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>419</v>
+        <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8750,21 +8931,19 @@
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>423</v>
+        <v>84</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>424</v>
+        <v>85</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>425</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>20</v>
       </c>
@@ -8812,7 +8991,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>426</v>
+        <v>86</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>74</v>
@@ -8821,35 +9000,35 @@
         <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>427</v>
+        <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>428</v>
+        <v>87</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>420</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -8858,23 +9037,21 @@
         <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>256</v>
+        <v>89</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>431</v>
+        <v>166</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>432</v>
+        <v>167</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>20</v>
       </c>
@@ -8910,45 +9087,45 @@
         <v>20</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>435</v>
+        <v>95</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>436</v>
+        <v>87</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>420</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8971,19 +9148,17 @@
         <v>126</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>438</v>
+        <v>116</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -9008,13 +9183,13 @@
         <v>20</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>20</v>
+        <v>431</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>20</v>
+        <v>432</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>20</v>
@@ -9032,7 +9207,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>74</v>
@@ -9047,18 +9222,18 @@
         <v>79</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>443</v>
+        <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>444</v>
+        <v>433</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9081,19 +9256,19 @@
         <v>126</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -9130,19 +9305,17 @@
         <v>20</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="AC68" s="2"/>
       <c r="AD68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>74</v>
@@ -9157,20 +9330,22 @@
         <v>79</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>451</v>
+        <v>419</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>452</v>
+        <v>440</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="D69" t="s" s="2">
         <v>20</v>
       </c>
@@ -9182,7 +9357,7 @@
         <v>82</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>20</v>
@@ -9191,19 +9366,19 @@
         <v>126</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>454</v>
+        <v>230</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -9252,7 +9427,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>74</v>
@@ -9264,23 +9439,25 @@
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>459</v>
+        <v>79</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>460</v>
+        <v>419</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>20</v>
+        <v>440</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="D70" t="s" s="2">
         <v>20</v>
       </c>
@@ -9292,7 +9469,7 @@
         <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>20</v>
@@ -9301,17 +9478,19 @@
         <v>126</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="O70" t="s" s="2">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -9360,29 +9539,1225 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AG70" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AL70" t="s" s="2">
+      <c r="B74" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q74" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="R74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="Y75" s="2"/>
+      <c r="Z75" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AL81" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL70">
+  <autoFilter ref="A1:AL81">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9392,7 +10767,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI80">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-timed-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
